--- a/data/trans_dic/IP2004-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les sangran las encías</t>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 13,24</t>
+          <t>3,68; 12,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,58</t>
+          <t>1,68; 9,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,77</t>
+          <t>1,37; 12,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 11,23</t>
+          <t>2,43; 11,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,25</t>
+          <t>2,93; 13,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,81</t>
+          <t>0,89; 7,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,57</t>
+          <t>1,42; 11,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,06</t>
+          <t>4,09; 10,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,47</t>
+          <t>3,36; 9,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,28</t>
+          <t>1,61; 7,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,2</t>
+          <t>0,82; 7,4</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 5,12</t>
+          <t>1,98; 4,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,88</t>
+          <t>1,83; 4,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,83</t>
+          <t>1,97; 4,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,8</t>
+          <t>0,68; 2,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,25</t>
+          <t>2,4; 5,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,58</t>
+          <t>1,23; 3,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,29</t>
+          <t>1,0; 3,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,31</t>
+          <t>1,06; 3,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,56</t>
+          <t>2,56; 4,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,64</t>
+          <t>1,77; 3,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,5</t>
+          <t>1,74; 3,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,6</t>
+          <t>1,07; 2,61</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,33</t>
+          <t>0,49; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,76</t>
+          <t>0,87; 5,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,69</t>
+          <t>0,34; 3,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,75</t>
+          <t>1,07; 5,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,48</t>
+          <t>0,26; 2,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,42</t>
+          <t>0,65; 3,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,13</t>
+          <t>0,21; 2,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,32</t>
+          <t>0,64; 3,45</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,76</t>
+          <t>2,41; 4,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,4</t>
+          <t>2,1; 4,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,05</t>
+          <t>1,89; 4,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,09</t>
+          <t>0,61; 2,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,37</t>
+          <t>2,11; 4,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,6</t>
+          <t>1,54; 3,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,5</t>
+          <t>0,94; 2,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,43</t>
+          <t>1,46; 3,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,15</t>
+          <t>2,6; 4,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,67</t>
+          <t>2,08; 3,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,94</t>
+          <t>1,61; 2,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,5</t>
+          <t>1,23; 2,44</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6635</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2857</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4798</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5797</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>11434</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9979</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4845</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3214</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3224; 11281</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1491; 8436</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>770; 6822</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1951</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1997; 9498</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2422; 11555</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>600; 5341</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>851; 7163</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6935; 17910</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5761; 16962</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1991; 9442</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>928; 8398</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12372</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12910</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13732</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6567</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10067</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8748</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9544</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>29122</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>22977</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>22480</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>16111</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7792; 18863</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7675; 20528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8671; 21915</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3099; 12914</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10816; 23703</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5685; 16533</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4623; 14767</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5376; 16197</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>21668; 37909</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>15626; 31864</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>15770; 31728</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>10307; 24987</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3043</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3864</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4690</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3043</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>5119</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5382</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>784; 7617</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1345; 8429</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>546; 5699</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4001</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3940</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4008</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1956; 10648</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>793; 7734</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2036; 9941</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>705; 7464</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2118; 11375</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>22051</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20955</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18592</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7651</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>17057</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>43599</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>38075</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30040</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>24707</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>15475; 30453</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>13929; 29559</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12479; 26752</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4010; 14776</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>14335; 29172</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10797; 25865</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6607; 17323</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>10934; 26191</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>34351; 54324</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>28324; 49273</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>21945; 40238</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>17266; 34185</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2004-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,89</t>
+          <t>3,98; 13,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,5</t>
+          <t>1,61; 9,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 12,13</t>
+          <t>1,41; 12,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 11,57</t>
+          <t>2,45; 11,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 13,98</t>
+          <t>3,15; 13,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,93</t>
+          <t>0,93; 8,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,98</t>
+          <t>1,4; 12,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,56</t>
+          <t>3,94; 10,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,9</t>
+          <t>3,3; 10,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,64</t>
+          <t>1,63; 7,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,4</t>
+          <t>0,83; 7,33</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,78</t>
+          <t>1,97; 4,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,91</t>
+          <t>1,89; 4,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,98</t>
+          <t>1,89; 4,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,85</t>
+          <t>0,72; 2,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,25</t>
+          <t>2,32; 5,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,57</t>
+          <t>1,15; 3,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,18</t>
+          <t>0,97; 3,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,2</t>
+          <t>1,03; 3,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,48</t>
+          <t>2,53; 4,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,62</t>
+          <t>1,83; 3,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,51</t>
+          <t>1,77; 3,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,61</t>
+          <t>1,07; 2,55</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,72</t>
+          <t>0,46; 4,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,43</t>
+          <t>0,97; 5,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,52</t>
+          <t>0,33; 3,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,85</t>
+          <t>1,07; 5,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,51</t>
+          <t>0,26; 2,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,2</t>
+          <t>0,69; 3,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,25</t>
+          <t>0,21; 2,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,45</t>
+          <t>0,69; 3,44</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,73</t>
+          <t>2,34; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,46</t>
+          <t>2,2; 4,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,06</t>
+          <t>1,91; 4,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,26</t>
+          <t>0,62; 2,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,29</t>
+          <t>2,31; 4,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,69</t>
+          <t>1,62; 3,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,47</t>
+          <t>0,97; 2,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,5</t>
+          <t>1,44; 3,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,11</t>
+          <t>2,55; 4,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,61</t>
+          <t>2,12; 3,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,96</t>
+          <t>1,66; 2,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,44</t>
+          <t>1,17; 2,48</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3224; 11281</t>
+          <t>3481; 11906</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1491; 8436</t>
+          <t>1429; 8440</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>770; 6822</t>
+          <t>796; 7122</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>0; 2536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1997; 9498</t>
+          <t>2014; 9758</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2422; 11555</t>
+          <t>2605; 11304</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>600; 5341</t>
+          <t>623; 5930</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>851; 7163</t>
+          <t>837; 7556</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6935; 17910</t>
+          <t>6690; 17676</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5761; 16962</t>
+          <t>5658; 17345</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1991; 9442</t>
+          <t>2018; 9195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>928; 8398</t>
+          <t>943; 8320</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7792; 18863</t>
+          <t>7755; 19208</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7675; 20528</t>
+          <t>7893; 20256</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8671; 21915</t>
+          <t>8334; 21128</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3099; 12914</t>
+          <t>3251; 13278</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10816; 23703</t>
+          <t>10453; 23746</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5685; 16533</t>
+          <t>5322; 16840</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4623; 14767</t>
+          <t>4515; 14831</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5376; 16197</t>
+          <t>5213; 16795</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21668; 37909</t>
+          <t>21370; 38642</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15626; 31864</t>
+          <t>16127; 32804</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15770; 31728</t>
+          <t>15977; 31339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10307; 24987</t>
+          <t>10265; 24438</t>
         </is>
       </c>
     </row>
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>784; 7617</t>
+          <t>744; 7545</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1345; 8429</t>
+          <t>1511; 8360</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>546; 5699</t>
+          <t>540; 5726</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4001</t>
+          <t>0; 3565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,37 +1945,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3940</t>
+          <t>0; 4414</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4008</t>
+          <t>0; 4370</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1956; 10648</t>
+          <t>1956; 10626</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>793; 7734</t>
+          <t>788; 7589</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2036; 9941</t>
+          <t>2139; 10243</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>705; 7464</t>
+          <t>710; 7077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2118; 11375</t>
+          <t>2273; 11347</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15475; 30453</t>
+          <t>15021; 30106</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13929; 29559</t>
+          <t>14564; 29592</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12479; 26752</t>
+          <t>12574; 27149</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4010; 14776</t>
+          <t>4089; 13569</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14335; 29172</t>
+          <t>15694; 30303</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10797; 25865</t>
+          <t>11382; 25529</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6607; 17323</t>
+          <t>6782; 17999</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10934; 26191</t>
+          <t>10765; 25750</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34351; 54324</t>
+          <t>33704; 55602</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28324; 49273</t>
+          <t>28908; 50162</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21945; 40238</t>
+          <t>22538; 40371</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17266; 34185</t>
+          <t>16394; 34711</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2004-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,58%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,08%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 13,6</t>
+          <t>2,37; 11,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,51</t>
+          <t>2,58; 13,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,66</t>
+          <t>0,89; 7,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>1,6; 13,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 11,89</t>
+          <t>3,76; 13,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,68</t>
+          <t>2,17; 9,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,8</t>
+          <t>1,34; 11,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,63</t>
+          <t>0,0; 4,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,42</t>
+          <t>3,95; 10,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 10,12</t>
+          <t>2,94; 9,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,44</t>
+          <t>1,48; 7,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,33</t>
+          <t>0,95; 8,4</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,12%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,87</t>
+          <t>2,46; 5,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,84</t>
+          <t>1,28; 3,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,8</t>
+          <t>1,02; 3,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,93</t>
+          <t>1,03; 3,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,26</t>
+          <t>1,94; 5,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,64</t>
+          <t>1,94; 4,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,2</t>
+          <t>2,02; 4,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,32</t>
+          <t>0,78; 3,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,57</t>
+          <t>2,51; 4,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,72</t>
+          <t>1,83; 3,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,47</t>
+          <t>1,7; 3,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,55</t>
+          <t>1,09; 2,64</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,39</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,53</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>1,02; 5,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,46; 4,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,91; 5,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,34; 3,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,84</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,46</t>
+          <t>0,24; 2,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,29</t>
+          <t>0,72; 3,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,13</t>
+          <t>0,25; 2,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,44</t>
+          <t>0,69; 3,22</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,68</t>
+          <t>2,22; 4,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,47</t>
+          <t>1,57; 3,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,12</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,07</t>
+          <t>1,51; 3,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,46</t>
+          <t>2,37; 4,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,64</t>
+          <t>2,21; 4,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,57</t>
+          <t>1,87; 4,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,44</t>
+          <t>0,62; 2,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,2</t>
+          <t>2,56; 4,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,68</t>
+          <t>2,1; 3,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,97</t>
+          <t>1,57; 2,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,48</t>
+          <t>1,27; 2,6</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4798</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2886</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>6635</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4182</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2857</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4798</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1988</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>340</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3226</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3481; 11906</t>
+          <t>1948; 9222</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1429; 8440</t>
+          <t>2135; 10950</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>796; 7122</t>
+          <t>603; 5260</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2536</t>
+          <t>878; 7523</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2014; 9758</t>
+          <t>3294; 11585</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2605; 11304</t>
+          <t>1929; 8507</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>623; 5930</t>
+          <t>752; 6623</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>837; 7556</t>
+          <t>0; 2121</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6690; 17676</t>
+          <t>6708; 17057</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5658; 17345</t>
+          <t>5039; 16229</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2018; 9195</t>
+          <t>1832; 9006</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>943; 8320</t>
+          <t>954; 8469</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10067</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8748</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8478</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12372</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12910</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13732</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6567</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10067</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8748</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>15321</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7755; 19208</t>
+          <t>11101; 23693</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7893; 20256</t>
+          <t>5902; 16580</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8334; 21128</t>
+          <t>4745; 15266</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3251; 13278</t>
+          <t>4811; 15040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10453; 23746</t>
+          <t>7668; 20208</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5322; 16840</t>
+          <t>8116; 20414</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4515; 14831</t>
+          <t>8899; 21254</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5213; 16795</t>
+          <t>3328; 13431</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21370; 38642</t>
+          <t>21210; 38539</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16127; 32804</t>
+          <t>16158; 32067</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15977; 31339</t>
+          <t>15403; 31660</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10265; 24438</t>
+          <t>9692; 23586</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4264</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3043</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3864</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>771</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5035</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>744; 7545</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1511; 8360</t>
+          <t>0; 4449</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>540; 5726</t>
+          <t>0; 3547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3565</t>
+          <t>1707; 9314</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>736; 6988</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4414</t>
+          <t>1405; 8935</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4370</t>
+          <t>544; 5978</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1956; 10626</t>
+          <t>0; 3848</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>788; 7589</t>
+          <t>733; 7634</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2139; 10243</t>
+          <t>2253; 10627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>710; 7077</t>
+          <t>837; 7066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2273; 11347</t>
+          <t>2167; 10175</t>
         </is>
       </c>
     </row>
@@ -1997,37 +1997,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22051</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20955</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>18592</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17120</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11449</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23583</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15021; 30106</t>
+          <t>15087; 29696</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14564; 29592</t>
+          <t>10987; 25264</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12574; 27149</t>
+          <t>6984; 17556</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4089; 13569</t>
+          <t>10377; 23077</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15694; 30303</t>
+          <t>15223; 30597</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11382; 25529</t>
+          <t>14641; 29159</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6782; 17999</t>
+          <t>12341; 26686</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10765; 25750</t>
+          <t>3858; 13843</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33704; 55602</t>
+          <t>33813; 54857</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28908; 50162</t>
+          <t>28630; 50014</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22538; 40371</t>
+          <t>21326; 39957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16394; 34711</t>
+          <t>16571; 33984</t>
         </is>
       </c>
     </row>
